--- a/artfynd/A 39990-2026 artfynd.xlsx
+++ b/artfynd/A 39990-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193739</v>
       </c>
       <c r="B2" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137193204</v>
       </c>
       <c r="B3" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137193384</v>
       </c>
       <c r="B4" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137193699</v>
       </c>
       <c r="B5" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137193722</v>
       </c>
       <c r="B6" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39990-2026 artfynd.xlsx
+++ b/artfynd/A 39990-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193739</v>
       </c>
       <c r="B2" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137193204</v>
       </c>
       <c r="B3" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137193384</v>
       </c>
       <c r="B4" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137193699</v>
       </c>
       <c r="B5" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137193722</v>
       </c>
       <c r="B6" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137193686</v>
       </c>
       <c r="B7" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 39990-2026 artfynd.xlsx
+++ b/artfynd/A 39990-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193739</v>
       </c>
       <c r="B2" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137193204</v>
       </c>
       <c r="B3" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137193384</v>
       </c>
       <c r="B4" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137193699</v>
       </c>
       <c r="B5" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137193722</v>
       </c>
       <c r="B6" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137193686</v>
       </c>
       <c r="B7" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 39990-2026 artfynd.xlsx
+++ b/artfynd/A 39990-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,32 +792,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>137193204</v>
+        <v>137264317</v>
       </c>
       <c r="B3" t="n">
-        <v>79260</v>
+        <v>79503</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483953</v>
+        <v>483879</v>
       </c>
       <c r="R3" t="n">
-        <v>6828778</v>
+        <v>6828742</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -860,19 +860,9 @@
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:32</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,38 +888,38 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137193204</t>
+          <t>https://artportalen.se/Sighting/137264317</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137193384</v>
+        <v>137264538</v>
       </c>
       <c r="B4" t="n">
-        <v>79260</v>
+        <v>79503</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484021</v>
+        <v>484004</v>
       </c>
       <c r="R4" t="n">
-        <v>6828808</v>
+        <v>6828730</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -972,19 +962,9 @@
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,13 +990,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137193384</t>
+          <t>https://artportalen.se/Sighting/137264538</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137193699</v>
+        <v>137193204</v>
       </c>
       <c r="B5" t="n">
         <v>79260</v>
@@ -1051,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484026</v>
+        <v>483953</v>
       </c>
       <c r="R5" t="n">
-        <v>6828708</v>
+        <v>6828778</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1086,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,13 +1102,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137193699</t>
+          <t>https://artportalen.se/Sighting/137193204</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137193722</v>
+        <v>137193384</v>
       </c>
       <c r="B6" t="n">
         <v>79260</v>
@@ -1163,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>484047</v>
+        <v>484021</v>
       </c>
       <c r="R6" t="n">
-        <v>6828694</v>
+        <v>6828808</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1198,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,16 +1214,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137193722</t>
+          <t>https://artportalen.se/Sighting/137193384</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137193686</v>
+        <v>137193699</v>
       </c>
       <c r="B7" t="n">
-        <v>58184</v>
+        <v>79260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1231,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1323,11 +1303,6 @@
           <t>16:03</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Talltitor och tofsmesar</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1350,6 +1325,338 @@
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137193699</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137193722</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kanervabäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>484047</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6828694</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137193722</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137264509</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58023</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kanervabäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>484070</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6828800</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137264509</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137193686</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58184</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kanervabäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>484026</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6828708</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Talltitor och tofsmesar</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137193686</t>
         </is>
@@ -1363,6 +1670,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39990-2026 artfynd.xlsx
+++ b/artfynd/A 39990-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193739</v>
       </c>
       <c r="B2" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137264317</v>
       </c>
       <c r="B3" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137264538</v>
       </c>
       <c r="B4" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>137193204</v>
       </c>
       <c r="B5" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137193384</v>
       </c>
       <c r="B6" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>137193699</v>
       </c>
       <c r="B7" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>137193722</v>
       </c>
       <c r="B8" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>137264509</v>
       </c>
       <c r="B9" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>137193686</v>
       </c>
       <c r="B10" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 39990-2026 artfynd.xlsx
+++ b/artfynd/A 39990-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193739</v>
       </c>
       <c r="B2" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137264317</v>
       </c>
       <c r="B3" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137264538</v>
       </c>
       <c r="B4" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>137193204</v>
       </c>
       <c r="B5" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137193384</v>
       </c>
       <c r="B6" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>137193699</v>
       </c>
       <c r="B7" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>137193722</v>
       </c>
       <c r="B8" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>137264509</v>
       </c>
       <c r="B9" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>137193686</v>
       </c>
       <c r="B10" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 39990-2026 artfynd.xlsx
+++ b/artfynd/A 39990-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193739</v>
       </c>
       <c r="B2" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137264317</v>
       </c>
       <c r="B3" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137264538</v>
       </c>
       <c r="B4" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>137193204</v>
       </c>
       <c r="B5" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137193384</v>
       </c>
       <c r="B6" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>137193699</v>
       </c>
       <c r="B7" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>137193722</v>
       </c>
       <c r="B8" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>137264509</v>
       </c>
       <c r="B9" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>137193686</v>
       </c>
       <c r="B10" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 39990-2026 artfynd.xlsx
+++ b/artfynd/A 39990-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193739</v>
       </c>
       <c r="B2" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137264317</v>
       </c>
       <c r="B3" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137264538</v>
       </c>
       <c r="B4" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>137193204</v>
       </c>
       <c r="B5" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137193384</v>
       </c>
       <c r="B6" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>137193699</v>
       </c>
       <c r="B7" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>137193722</v>
       </c>
       <c r="B8" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 39990-2026 artfynd.xlsx
+++ b/artfynd/A 39990-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193739</v>
       </c>
       <c r="B2" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137264317</v>
       </c>
       <c r="B3" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137264538</v>
       </c>
       <c r="B4" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>137193204</v>
       </c>
       <c r="B5" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137193384</v>
       </c>
       <c r="B6" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>137193699</v>
       </c>
       <c r="B7" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>137193722</v>
       </c>
       <c r="B8" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 39990-2026 artfynd.xlsx
+++ b/artfynd/A 39990-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193739</v>
       </c>
       <c r="B2" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137264317</v>
       </c>
       <c r="B3" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137264538</v>
       </c>
       <c r="B4" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>137193204</v>
       </c>
       <c r="B5" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137193384</v>
       </c>
       <c r="B6" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>137193699</v>
       </c>
       <c r="B7" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>137193722</v>
       </c>
       <c r="B8" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 39990-2026 artfynd.xlsx
+++ b/artfynd/A 39990-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193739</v>
       </c>
       <c r="B2" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137264317</v>
       </c>
       <c r="B3" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137264538</v>
       </c>
       <c r="B4" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>137193204</v>
       </c>
       <c r="B5" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137193384</v>
       </c>
       <c r="B6" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>137193699</v>
       </c>
       <c r="B7" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>137193722</v>
       </c>
       <c r="B8" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>137264509</v>
       </c>
       <c r="B9" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>137193686</v>
       </c>
       <c r="B10" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
